--- a/investment_plan.xlsx
+++ b/investment_plan.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>美股ETF投资仪表盘</t>
   </si>
@@ -1024,16 +1024,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.174307418927337</c:v>
+                  <c:v>0.253012219355848</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.701188175551174</c:v>
+                  <c:v>0.580119517350817</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0735682158189545</c:v>
+                  <c:v>0.125068072048105</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0509361897025352</c:v>
+                  <c:v>0.0418001912452304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B2">
         <f>SUM(持仓汇总!B2:B5)</f>
-        <v>1755.77</v>
+        <v>2144.66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B3">
         <f>SUM(持仓汇总!E2:E5)</f>
-        <v>1722.61610320153</v>
+        <v>2099.11720505171</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B4">
         <f>B3-B2</f>
-        <v>-33.1538967984707</v>
+        <v>-45.5427949482887</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B7">
         <f>持仓汇总!F2</f>
-        <v>0.174307418927337</v>
+        <v>0.253012219355848</v>
       </c>
       <c r="C7">
         <f>持仓汇总!G2</f>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B8">
         <f>持仓汇总!F3</f>
-        <v>0.701188175551174</v>
+        <v>0.580119517350817</v>
       </c>
       <c r="C8">
         <f>持仓汇总!G3</f>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B9">
         <f>持仓汇总!F4</f>
-        <v>0.0735682158189545</v>
+        <v>0.125068072048105</v>
       </c>
       <c r="C9">
         <f>持仓汇总!G4</f>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D9" t="str">
         <f>IF(B9&lt;C9-0.03,"低配补仓",IF(B9&gt;C9+0.03,"高配减少","正常"))</f>
-        <v>低配补仓</v>
+        <v>正常</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B10">
         <f>持仓汇总!F5</f>
-        <v>0.0509361897025352</v>
+        <v>0.0418001912452304</v>
       </c>
       <c r="C10">
         <f>持仓汇总!G5</f>
@@ -1916,48 +1916,80 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="E15" s="9" t="str">
-        <f t="shared" ref="E2:E65" si="1">IF(C15="","",C15/D15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="9" t="str">
+      <c r="A15" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="9">
+        <v>111.33</v>
+      </c>
+      <c r="F15" s="9">
+        <v>37.11</v>
+      </c>
+      <c r="G15" s="9">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="E16" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G16" s="9" t="str">
+      <c r="A16" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="9">
+        <v>28.66</v>
+      </c>
+      <c r="F16" s="9">
+        <v>37.11</v>
+      </c>
+      <c r="G16" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="5:7">
-      <c r="E17" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G17" s="9" t="str">
+        <v>0.772298571813527</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="9">
+        <v>238.93</v>
+      </c>
+      <c r="F17" s="9">
+        <v>708.6</v>
+      </c>
+      <c r="G17" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="5:7">
-      <c r="E18" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G18" s="9" t="str">
+        <v>0.337186000564493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="16">
+        <v>46240</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="9">
+        <v>9.97</v>
+      </c>
+      <c r="F18" s="9">
+        <v>295.86</v>
+      </c>
+      <c r="G18" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="5:7">
+        <v>0.0336983708510782</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="E19" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E2:E65" si="1">IF(C19="","",C19/D19)</f>
         <v/>
       </c>
       <c r="G19" s="9" t="str">
@@ -1965,7 +1997,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="5:7">
+    <row r="20" spans="1:7">
       <c r="E20" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1975,7 +2007,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="5:7">
+    <row r="21" spans="1:7">
       <c r="E21" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1985,7 +2017,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="5:7">
+    <row r="22" spans="1:7">
       <c r="E22" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1995,7 +2027,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="5:7">
+    <row r="23" spans="1:7">
       <c r="E23" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2005,7 +2037,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="5:7">
+    <row r="24" spans="1:7">
       <c r="E24" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2015,7 +2047,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="5:7">
+    <row r="25" spans="1:7">
       <c r="E25" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2025,7 +2057,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="5:7">
+    <row r="26" spans="1:7">
       <c r="E26" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2035,7 +2067,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="5:7">
+    <row r="27" spans="1:7">
       <c r="E27" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2045,7 +2077,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="5:7">
+    <row r="28" spans="1:7">
       <c r="E28" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2055,7 +2087,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="5:7">
+    <row r="29" spans="1:7">
       <c r="E29" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2065,7 +2097,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="5:7">
+    <row r="30" spans="1:7">
       <c r="E30" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2075,7 +2107,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="5:7">
+    <row r="31" spans="1:7">
       <c r="E31" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2085,7 +2117,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="5:7">
+    <row r="32" spans="1:7">
       <c r="E32" s="9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -6833,29 +6865,29 @@
       </c>
       <c r="B2" s="2">
         <f>SUMIF(交易记录!B:B,A2,交易记录!E:E)</f>
-        <v>302.89</v>
+        <v>541.82</v>
       </c>
       <c r="C2" s="2">
         <f>SUMIF(交易记录!B:B,A2,交易记录!G:G)</f>
-        <v>0.438598841296706</v>
+        <v>0.7757848418612</v>
       </c>
       <c r="D2" s="6">
         <v>684.6</v>
       </c>
       <c r="E2" s="2">
         <f>IF(D2="","",C2*D2)</f>
-        <v>300.264766751725</v>
+        <v>531.102302738177</v>
       </c>
       <c r="F2" s="2">
         <f>IF(SUM(E:E)=0,"",E2/SUM(E:E))</f>
-        <v>0.174307418927337</v>
+        <v>0.253012219355848</v>
       </c>
       <c r="G2" s="2">
         <v>0.4</v>
       </c>
       <c r="H2" s="2">
         <f>F2-G2</f>
-        <v>-0.225692581072663</v>
+        <v>-0.146987780644152</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6864,29 +6896,29 @@
       </c>
       <c r="B3" s="2">
         <f>SUMIF(交易记录!B:B,A3,交易记录!E:E)</f>
-        <v>1231.17</v>
+        <v>1241.14</v>
       </c>
       <c r="C3" s="2">
         <f>SUMIF(交易记录!B:B,A3,交易记录!G:G)</f>
-        <v>4.12780412336461</v>
+        <v>4.16150249421569</v>
       </c>
       <c r="D3" s="6">
         <v>292.62</v>
       </c>
       <c r="E3" s="2">
         <f>IF(D3="","",C3*D3)</f>
-        <v>1207.87804257895</v>
+        <v>1217.7388598574</v>
       </c>
       <c r="F3" s="2">
         <f>IF(SUM(E:E)=0,"",E3/SUM(E:E))</f>
-        <v>0.701188175551174</v>
+        <v>0.580119517350817</v>
       </c>
       <c r="G3" s="2">
         <v>0.35</v>
       </c>
       <c r="H3" s="2">
         <f>F3-G3</f>
-        <v>0.351188175551174</v>
+        <v>0.230119517350817</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6895,29 +6927,29 @@
       </c>
       <c r="B4" s="2">
         <f>SUMIF(交易记录!B:B,A4,交易记录!E:E)</f>
-        <v>130.72</v>
+        <v>270.71</v>
       </c>
       <c r="C4" s="2">
         <f>SUMIF(交易记录!B:B,A4,交易记录!G:G)</f>
-        <v>3.52027203482046</v>
+        <v>7.29257060663398</v>
       </c>
       <c r="D4" s="6">
         <v>36</v>
       </c>
       <c r="E4" s="2">
         <f>IF(D4="","",C4*D4)</f>
-        <v>126.729793253536</v>
+        <v>262.532541838823</v>
       </c>
       <c r="F4" s="2">
         <f>IF(SUM(E:E)=0,"",E4/SUM(E:E))</f>
-        <v>0.0735682158189545</v>
+        <v>0.125068072048105</v>
       </c>
       <c r="G4" s="2">
         <v>0.15</v>
       </c>
       <c r="H4" s="2">
         <f>F4-G4</f>
-        <v>-0.0764317841810455</v>
+        <v>-0.0249319279518954</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6941,14 +6973,14 @@
       </c>
       <c r="F5" s="2">
         <f>IF(SUM(E:E)=0,"",E5/SUM(E:E))</f>
-        <v>0.0509361897025352</v>
+        <v>0.0418001912452304</v>
       </c>
       <c r="G5" s="2">
         <v>0.05</v>
       </c>
       <c r="H5" s="2">
         <f>F5-G5</f>
-        <v>0.000936189702535228</v>
+        <v>-0.00819980875476957</v>
       </c>
     </row>
   </sheetData>
@@ -6999,7 +7031,7 @@
       </c>
       <c r="B2" s="2">
         <f>持仓汇总!F2</f>
-        <v>0.174307418927337</v>
+        <v>0.253012219355848</v>
       </c>
       <c r="C2" s="2">
         <f>持仓汇总!G2</f>
@@ -7007,11 +7039,11 @@
       </c>
       <c r="D2" s="2">
         <f>MAX(0,C2-B2)</f>
-        <v>0.225692581072663</v>
+        <v>0.146987780644152</v>
       </c>
       <c r="E2" s="2">
         <f>IF(SUM(D2:D5)=0,参数设置!B3*C2,参数设置!B3*D2/SUM(D2:D5))</f>
-        <v>2241.05640288036</v>
+        <v>2448.17079469293</v>
       </c>
       <c r="F2" t="str">
         <f>IF(D2&gt;0.03,"重点补仓",IF(D2&gt;0,"增加","减少"))</f>
@@ -7019,7 +7051,7 @@
       </c>
       <c r="G2" s="3">
         <f>E2/参数设置!B2</f>
-        <v>287.314923446201</v>
+        <v>313.868050601658</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -7029,7 +7061,7 @@
       </c>
       <c r="B3" s="2">
         <f>持仓汇总!F3</f>
-        <v>0.701188175551174</v>
+        <v>0.580119517350817</v>
       </c>
       <c r="C3" s="2">
         <f>持仓汇总!G3</f>
@@ -7059,7 +7091,7 @@
       </c>
       <c r="B4" s="2">
         <f>持仓汇总!F4</f>
-        <v>0.0735682158189545</v>
+        <v>0.125068072048105</v>
       </c>
       <c r="C4" s="2">
         <f>持仓汇总!G4</f>
@@ -7067,19 +7099,19 @@
       </c>
       <c r="D4" s="2">
         <f>MAX(0,C4-B4)</f>
-        <v>0.0764317841810455</v>
+        <v>0.0249319279518954</v>
       </c>
       <c r="E4" s="2">
         <f>IF(SUM(D2:D5)=0,参数设置!B3*C4,参数设置!B3*D4/SUM(D2:D5))</f>
-        <v>758.943597119636</v>
+        <v>415.256408388031</v>
       </c>
       <c r="F4" t="str">
         <f>IF(D4&gt;0.03,"重点补仓",IF(D4&gt;0,"增加","减少"))</f>
-        <v>重点补仓</v>
+        <v>增加</v>
       </c>
       <c r="G4" s="3">
         <f>E4/参数设置!B2</f>
-        <v>97.3004611691841</v>
+        <v>53.2380010753886</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7089,7 +7121,7 @@
       </c>
       <c r="B5" s="2">
         <f>持仓汇总!F5</f>
-        <v>0.0509361897025352</v>
+        <v>0.0418001912452304</v>
       </c>
       <c r="C5" s="2">
         <f>持仓汇总!G5</f>
@@ -7097,19 +7129,19 @@
       </c>
       <c r="D5" s="2">
         <f>MAX(0,C5-B5)</f>
-        <v>0</v>
+        <v>0.00819980875476957</v>
       </c>
       <c r="E5" s="2">
         <f>IF(SUM(D2:D5)=0,参数设置!B3*C5,参数设置!B3*D5/SUM(D2:D5))</f>
-        <v>0</v>
+        <v>136.57279691904</v>
       </c>
       <c r="F5" t="str">
         <f>IF(D5&gt;0.03,"重点补仓",IF(D5&gt;0,"增加","减少"))</f>
-        <v>减少</v>
+        <v>增加</v>
       </c>
       <c r="G5" s="3">
         <f>E5/参数设置!B2</f>
-        <v>0</v>
+        <v>17.5093329383385</v>
       </c>
     </row>
   </sheetData>
